--- a/hasil_cluster_som.xlsx
+++ b/hasil_cluster_som.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Produksi_Beras</t>
+          <t>Produksi_Padi</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -533,11 +533,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-14</t>
+          <t>17-4</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -578,11 +578,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -623,11 +623,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-5</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -668,11 +668,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-7</t>
+          <t>15-3</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -713,11 +713,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-4</t>
+          <t>15-5</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -758,11 +758,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0-15</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -803,11 +803,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>13-2</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -848,11 +848,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6-17</t>
+          <t>13-1</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -893,11 +893,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7-0</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -938,11 +938,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-7</t>
+          <t>14-2</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -983,11 +983,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-11</t>
+          <t>14-0</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1028,11 +1028,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-5</t>
+          <t>15-5</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1073,11 +1073,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0-6</t>
+          <t>17-8</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1118,11 +1118,11 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7-16</t>
+          <t>16-0</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17-13</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1208,11 +1208,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15-8</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>5-11</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1298,11 +1298,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12-6</t>
+          <t>13-9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10-10</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1433,11 +1433,11 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13-6</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1478,11 +1478,11 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13-5</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1523,11 +1523,11 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6-14</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1568,11 +1568,11 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0-8</t>
+          <t>17-10</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1613,11 +1613,11 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4-15</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13-17</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>12-16</t>
+          <t>5-16</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -1793,11 +1793,11 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17-16</t>
+          <t>15-18</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1838,11 +1838,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8-17</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>15-8</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1928,11 +1928,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13-8</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>19-16</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2018,11 +2018,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17-16</t>
+          <t>0-19</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2063,11 +2063,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11-8</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16-1</t>
+          <t>5-14</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2153,11 +2153,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0-8</t>
+          <t>18-10</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>17-17</t>
+          <t>0-18</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2333,11 +2333,11 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>12-9</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2378,11 +2378,11 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>16-8</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>15-15</t>
+          <t>4-17</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>19-7</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3-14</t>
+          <t>0-16</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2558,11 +2558,11 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>15-0</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2603,11 +2603,11 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0-7</t>
+          <t>18-9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0-7</t>
+          <t>19-9</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0-11</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2738,11 +2738,11 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>15-13</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2783,11 +2783,11 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2828,11 +2828,11 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>14-15</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>15-16</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2918,11 +2918,11 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1-17</t>
+          <t>10-19</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>9-12</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3008,11 +3008,11 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>6-15</t>
+          <t>18-4</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3053,11 +3053,11 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>6-18</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3098,11 +3098,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>5-13</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -3188,11 +3188,11 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3-16</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>0-8</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -3278,11 +3278,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>1-8</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>6-13</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3413,11 +3413,11 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0-9</t>
+          <t>2-19</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>3-17</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -3548,11 +3548,11 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>4-16</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3593,11 +3593,11 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1-17</t>
+          <t>9-19</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>14-10</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3683,11 +3683,11 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>3-16</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>15-11</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3773,11 +3773,11 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>14-10</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3818,11 +3818,11 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2-17</t>
+          <t>10-18</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3863,11 +3863,11 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>9-18</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -3953,11 +3953,11 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>4-13</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>12-0</t>
+          <t>17-19</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4043,11 +4043,11 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>13-14</t>
+          <t>19-14</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -4088,11 +4088,11 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>14-4</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -4133,11 +4133,11 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>4-13</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -4178,11 +4178,11 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4223,11 +4223,11 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>14-3</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>11-14</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0-17</t>
+          <t>12-10</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4403,11 +4403,11 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>12-2</t>
+          <t>9-12</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>13-10</t>
+          <t>10-8</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>12-19</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>15-16</t>
+          <t>9-14</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4583,11 +4583,11 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>12-18</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>11-0</t>
+          <t>10-13</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4673,11 +4673,11 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>15-10</t>
+          <t>18-19</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4718,11 +4718,11 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>19-19</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4763,11 +4763,11 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>9-0</t>
+          <t>10-10</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>14-17</t>
+          <t>9-16</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -4853,11 +4853,11 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1-16</t>
+          <t>12-11</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4898,11 +4898,11 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>15-10</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>9-17</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>5-12</t>
+          <t>1-11</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -5033,11 +5033,11 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -5078,11 +5078,11 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>9-14</t>
+          <t>13-7</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -5123,11 +5123,11 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>17-9</t>
+          <t>13-5</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -5213,11 +5213,11 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -5258,11 +5258,11 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>17-7</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -5303,11 +5303,11 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>5-11</t>
+          <t>0-11</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8-8</t>
+          <t>13-7</t>
         </is>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>10-17</t>
+          <t>9-9</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -5438,11 +5438,11 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>17-0</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -5483,11 +5483,11 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>15-12</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>17-16</t>
         </is>
       </c>
       <c r="M113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5573,11 +5573,11 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>4-19</t>
         </is>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -5618,11 +5618,11 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>6-13</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -5663,11 +5663,11 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8-13</t>
+          <t>12-14</t>
         </is>
       </c>
       <c r="M116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>17-14</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -5753,11 +5753,11 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>9-15</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -5798,11 +5798,11 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>9-16</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -5843,11 +5843,11 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>10-15</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>10-15</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -5933,11 +5933,11 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>14-7</t>
         </is>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>15-7</t>
         </is>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -6023,11 +6023,11 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>10-16</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>14-11</t>
+          <t>6-15</t>
         </is>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -6113,11 +6113,11 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>1-11</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-8</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -6203,11 +6203,11 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>17-8</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>16-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -6293,11 +6293,11 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="M130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -6338,11 +6338,11 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="M131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -6383,11 +6383,11 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>16-12</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>18-6</t>
         </is>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -6473,11 +6473,11 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>5-9</t>
+          <t>0-9</t>
         </is>
       </c>
       <c r="M134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -6518,11 +6518,11 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>17-6</t>
         </is>
       </c>
       <c r="M135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -6563,11 +6563,11 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>13-9</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="M136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -6653,11 +6653,11 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>4-17</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="M138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -6698,11 +6698,11 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>11-17</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
@@ -6743,11 +6743,11 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>13-12</t>
         </is>
       </c>
       <c r="M140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>14-11</t>
         </is>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6833,11 +6833,11 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>18-1</t>
         </is>
       </c>
       <c r="M142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -6878,11 +6878,11 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>0-13</t>
         </is>
       </c>
       <c r="M143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
@@ -6923,11 +6923,11 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>19-12</t>
         </is>
       </c>
       <c r="M144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>15-17</t>
+          <t>8-15</t>
         </is>
       </c>
       <c r="M145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -7013,11 +7013,11 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -7058,11 +7058,11 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>0-13</t>
         </is>
       </c>
       <c r="M147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -7103,11 +7103,11 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>1-17</t>
+          <t>9-19</t>
         </is>
       </c>
       <c r="M148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>15-16</t>
+          <t>0-6</t>
         </is>
       </c>
       <c r="M149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -7193,11 +7193,11 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>13-1</t>
+          <t>18-12</t>
         </is>
       </c>
       <c r="M150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
@@ -7238,11 +7238,11 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>14-1</t>
+          <t>17-12</t>
         </is>
       </c>
       <c r="M151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -7283,11 +7283,11 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>13-12</t>
+          <t>12-16</t>
         </is>
       </c>
       <c r="M152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>14-2</t>
+          <t>17-13</t>
         </is>
       </c>
       <c r="M153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
@@ -7373,11 +7373,11 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>16-16</t>
         </is>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -7418,11 +7418,11 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>16-15</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
